--- a/hanbit_mvp_dataset_phase1/30_contract.xlsx
+++ b/hanbit_mvp_dataset_phase1/30_contract.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,26 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>contract_status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>plant_code</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>industry_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>company_size</t>
         </is>
       </c>
     </row>

--- a/hanbit_mvp_dataset_phase1/30_contract.xlsx
+++ b/hanbit_mvp_dataset_phase1/30_contract.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,11 @@
       <c r="O1" t="inlineStr">
         <is>
           <t>company_size</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>contract_agreement_date</t>
         </is>
       </c>
     </row>

--- a/hanbit_mvp_dataset_phase1/30_contract.xlsx
+++ b/hanbit_mvp_dataset_phase1/30_contract.xlsx
@@ -547,6 +547,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PL01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,6 +605,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PL01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,6 +658,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PL01</t>
         </is>
       </c>
     </row>
